--- a/asset-forge/products/pack_beauty_salon_sk.xlsx
+++ b/asset-forge/products/pack_beauty_salon_sk.xlsx
@@ -375,10 +375,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="18" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="17" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1441,7 +1441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.4" customWidth="1" min="1" max="1"/>
@@ -1560,36 +1560,36 @@
     <row r="11" ht="18" customHeight="1">
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>KONCOVÁ HOTOVOSŤ  ↗</t>
+          <t>TRŽBY VS PLÁN  ↗</t>
         </is>
       </c>
       <c r="D11" s="29" t="n"/>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>PRIEMERNÁ MARŽA OŠETRENÍ  ↗</t>
+          <t>KONCOVÁ HOTOVOSŤ  ↗</t>
         </is>
       </c>
       <c r="H11" s="29" t="n"/>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>PODIEL MIEZD  ↗</t>
+          <t>PRIEMERNÁ MARŽA OŠETRENÍ  ↗</t>
         </is>
       </c>
       <c r="L11" s="29" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="30">
+        <f>IFERROR('03 · Cash flow'!Q13,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="29" t="n"/>
+      <c r="F12" s="31">
         <f>IFERROR('03 · Cash flow'!N29,0)</f>
         <v/>
       </c>
-      <c r="D12" s="29" t="n"/>
-      <c r="F12" s="36">
+      <c r="H12" s="29" t="n"/>
+      <c r="J12" s="36">
         <f>IFERROR('04 · Marža ošetrení'!H30,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="29" t="n"/>
-      <c r="J12" s="37">
-        <f>IFERROR('05 · Zmeny'!I31,0)</f>
         <v/>
       </c>
       <c r="L12" s="29" t="n"/>
@@ -1606,138 +1606,167 @@
       <c r="L13" s="35" t="n"/>
     </row>
     <row r="14"/>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="15" ht="4" customHeight="1">
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>PODIEL MIEZD  ↗</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="37">
+        <f>IFERROR('05 · Zmeny'!I31,0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="29" t="n"/>
+    </row>
+    <row r="18" ht="14" customHeight="1">
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="35" t="n"/>
+    </row>
+    <row r="19"/>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>POSTREHY</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="B16" s="38">
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="B21" s="38">
         <f>IFERROR(IF('03 · Cash flow'!P13="","Tržby vs plán: zadajte ročný plán v hárku Cash flow.","Tržby vs plán: "&amp;TEXT('03 · Cash flow'!Q13,"#,##0 €")&amp;" ("&amp;TEXT('03 · Cash flow'!R13,"+0.0%;-0.0%")&amp;") — "&amp;IF('03 · Cash flow'!R13&gt;=0,"NAD plánom.","POD plánom, preverte hlavný zdroj tržieb.")),"Tržby vs plán: zatiaľ bez dát.")</f>
         <v/>
       </c>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
-      <c r="G16" s="21" t="n"/>
-      <c r="H16" s="21" t="n"/>
-      <c r="I16" s="21" t="n"/>
-      <c r="J16" s="21" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="21" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="39">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="39">
         <f>IFERROR("Čistá marža: "&amp;TEXT('03 · Cash flow'!O26/'03 · Cash flow'!O13,"0.0%")&amp;IF('03 · Cash flow'!O26/'03 · Cash flow'!O13&gt;=0.1," — zdravé."," — pozor, je nízka."),"Čistá marža: zatiaľ bez dát.")</f>
         <v/>
       </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
-      <c r="K17" s="21" t="n"/>
-      <c r="L17" s="21" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="38">
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="21" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="38">
         <f>IFERROR("Podiel miezd: "&amp;TEXT('05 · Zmeny'!I31,"0.0%")&amp;IF('05 · Zmeny'!I31&gt;0.35," — NAD cieľom 35 %."," — v poriadku."),"Podiel miezd: zatiaľ bez dát.")</f>
         <v/>
       </c>
-      <c r="C18" s="21" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
-      <c r="H18" s="21" t="n"/>
-      <c r="I18" s="21" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="39">
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="21" t="n"/>
+      <c r="L23" s="21" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="B24" s="39">
         <f>IFERROR("Položky pod cieľovou maržou: "&amp;TEXT('04 · Marža ošetrení'!H31,"0")&amp;".","Marža: zatiaľ bez dát.")</f>
         <v/>
       </c>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="21" t="n"/>
-      <c r="H19" s="21" t="n"/>
-      <c r="I19" s="21" t="n"/>
-      <c r="J19" s="21" t="n"/>
-      <c r="K19" s="21" t="n"/>
-      <c r="L19" s="21" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="38">
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="21" t="n"/>
+      <c r="L24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="B25" s="38">
         <f>IFERROR("Rozdiel v pokladni (rok): "&amp;TEXT('06 · Tržby'!H40,"#,##0.00 €")&amp;IF(ABS('06 · Tržby'!H40)&gt;1," — preverte."," — sedí."),"Pokladňa: zatiaľ bez dát.")</f>
         <v/>
       </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-      <c r="J20" s="21" t="n"/>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
-    </row>
-    <row r="21"/>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
+    </row>
+    <row r="26"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tieto čísla sa aktualizujú automaticky, keď vyplníte ostatné hárky.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="30">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B16:L16"/>
+    <mergeCell ref="B25:L25"/>
     <mergeCell ref="B22:L22"/>
     <mergeCell ref="B7:D8"/>
-    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="B27:L27"/>
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="F7:H8"/>
+    <mergeCell ref="B21:L21"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B12:D13"/>
+    <mergeCell ref="B15:D15"/>
     <mergeCell ref="F12:H13"/>
+    <mergeCell ref="B17:D18"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B17:L17"/>
+    <mergeCell ref="B23:L23"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B19:L19"/>
     <mergeCell ref="F11:H11"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="J5:L5"/>
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="J7:L8"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B15:L15"/>
+    <mergeCell ref="B24:L24"/>
     <mergeCell ref="B20:L20"/>
     <mergeCell ref="J12:L13"/>
   </mergeCells>
@@ -1746,7 +1775,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12">
+  <conditionalFormatting sqref="B17">
     <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="0">
       <formula>0.35</formula>
     </cfRule>
@@ -1758,6 +1787,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
